--- a/SLR/Full-Paper-Read/Paper-Review/PS15.xlsx
+++ b/SLR/Full-Paper-Read/Paper-Review/PS15.xlsx
@@ -11,24 +11,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
-  <authors>
-    <author/>
-  </authors>
-  <commentList>
-    <comment authorId="0" ref="I4">
-      <text>
-        <t xml:space="preserve">A safety-critical CPS based control system with unmanned wireless sensors, such as unmanned substation (of an electric power corporation) in a smart grid.
-	-Adnan Ashraf</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
   <si>
     <t>ID</t>
   </si>
@@ -42,24 +26,24 @@
     <t>The paper proposes the following contributions:</t>
   </si>
   <si>
-    <t>This paper proposes a systematic virtual networking architecture to perform the global virtualization control and monitoring of a CPS, in which network functions virtualization (NFV) configu- ration and orchestration can be realized.</t>
+    <t xml:space="preserve">The authors discsuss the complextiy of autonmous ecosystems and how existing approaches struggle in this context. The authors describe various challenges for safety assurance of these ecosystems, and describe a conceptual solution. </t>
+  </si>
+  <si>
+    <t>The paper discuss ecosystems from a very specific angle, and the paper is essentially just related work and a conceptual framework to be implemented, considering what the authors believe to be weaknesses in current approaches.</t>
+  </si>
+  <si>
+    <t>CPS Case Study / Example availability</t>
   </si>
   <si>
     <t>&lt;add your comment here if any&gt;</t>
   </si>
   <si>
-    <t>CPS Case Study / Example availability</t>
-  </si>
-  <si>
     <t>SECO Tools Availability (add repository or website in the comment)</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>architecture</t>
-  </si>
-  <si>
     <t>Related Challenge - See SPE paper (Write Others in comment cell)</t>
   </si>
   <si>
@@ -69,7 +53,7 @@
     <t>n.a.</t>
   </si>
   <si>
-    <t>systemc architecture + lifetime extension (there are two unresolved problems for a software- defined CPS. First, a feasible systemic architecture is a must for software-defined CPS, which should provide a global vir- tualization management and closed-loop control between the cyber side and the physical side in a CPS. Second, the life- time of a software-defined CPS scenario needs to be extended for critical applications. )</t>
+    <t>behaviour, trust, supervision, feedback. architecture</t>
   </si>
   <si>
     <t>Does it contribute to answer RQ1?</t>
@@ -87,16 +71,25 @@
     <t>Application Domain(s) (at least one or domain independent)</t>
   </si>
   <si>
-    <t>Application Domain Independent</t>
+    <t>Automotive</t>
+  </si>
+  <si>
+    <t>Autonomous systems, Safety-critical systems</t>
   </si>
   <si>
     <t>Quality Evaluation (From 1 to 10) - From "Quality" Tab</t>
   </si>
   <si>
+    <t>This is a short vision paper, so many of the criteria do not apply. It is well written, but very limited scope</t>
+  </si>
+  <si>
     <t>RQ1: In the SECO, what are the main challenges faced during the CPS development?</t>
   </si>
   <si>
     <t>RQ2: How do industry and academia collaborate and benefit in the SECO for CPS development?</t>
+  </si>
+  <si>
+    <t>Vision Paper</t>
   </si>
   <si>
     <t>Assessment Criterion (Question)</t>
@@ -202,7 +195,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -232,6 +225,11 @@
       <sz val="12.0"/>
       <color theme="1"/>
       <name val="Lato"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -566,7 +564,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="62">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -585,7 +583,7 @@
     <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="9" fillId="3" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -605,7 +603,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="16" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
@@ -629,9 +627,6 @@
     <xf borderId="19" fillId="5" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
     <xf borderId="21" fillId="3" fontId="1" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
@@ -641,72 +636,87 @@
     <xf borderId="18" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="18" fillId="5" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="22" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="22" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="23" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="23" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="24" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="24" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="25" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="24" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="25" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="24" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="25" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="24" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="24" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="25" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="25" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="25" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1023,7 +1033,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="17">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18"/>
@@ -1031,7 +1041,7 @@
       <c r="G4" s="18"/>
       <c r="H4" s="18"/>
       <c r="I4" s="19" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -1039,10 +1049,10 @@
         <v>3.0</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
@@ -1050,7 +1060,7 @@
       <c r="G5" s="18"/>
       <c r="H5" s="18"/>
       <c r="I5" s="21" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -1098,7 +1108,7 @@
       <c r="G7" s="25"/>
       <c r="H7" s="18"/>
       <c r="I7" s="26" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1109,7 +1119,7 @@
         <v>16</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="25"/>
@@ -1117,7 +1127,7 @@
       <c r="G8" s="25"/>
       <c r="H8" s="18"/>
       <c r="I8" s="26" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
@@ -1128,15 +1138,15 @@
         <v>17</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="25"/>
       <c r="F9" s="25"/>
       <c r="G9" s="25"/>
       <c r="H9" s="18"/>
-      <c r="I9" s="30" t="s">
-        <v>5</v>
+      <c r="I9" s="21" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
@@ -1146,26 +1156,26 @@
       <c r="B10" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="F10" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="G10" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="H10" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" s="26" t="s">
-        <v>5</v>
+      <c r="I10" s="23" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
@@ -1173,34 +1183,38 @@
         <v>9.0</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="33">
+        <v>21</v>
+      </c>
+      <c r="C11" s="32">
         <f>Quality!C29</f>
-        <v>10</v>
+        <v>6.111111111</v>
       </c>
       <c r="D11" s="25"/>
       <c r="E11" s="25"/>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
       <c r="H11" s="25"/>
-      <c r="I11" s="30" t="s">
-        <v>5</v>
+      <c r="I11" s="33" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1">
       <c r="B14" s="34" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="B15" s="34" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1"/>
-    <row r="17" ht="15.75" customHeight="1"/>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="B17" s="35" t="s">
+        <v>25</v>
+      </c>
+    </row>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>
     <row r="20" ht="15.75" customHeight="1"/>
@@ -2236,8 +2250,7 @@
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2256,362 +2269,362 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="35"/>
-      <c r="B1" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="C1" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="37"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="39"/>
+      <c r="A1" s="36"/>
+      <c r="B1" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="38"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="40"/>
     </row>
     <row r="2">
-      <c r="A2" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="41" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="42">
+      <c r="A2" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="43">
         <v>1.0</v>
       </c>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="43"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="44"/>
     </row>
     <row r="3">
-      <c r="A3" s="44"/>
-      <c r="B3" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="42">
+      <c r="A3" s="45"/>
+      <c r="B3" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="43">
         <v>1.0</v>
       </c>
-      <c r="D3" s="37"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="43"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="44"/>
     </row>
     <row r="4">
-      <c r="A4" s="44"/>
-      <c r="B4" s="41" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="42">
+      <c r="A4" s="45"/>
+      <c r="B4" s="42" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="43">
         <v>1.0</v>
       </c>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
     </row>
     <row r="5">
-      <c r="A5" s="44"/>
-      <c r="B5" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="42">
+      <c r="A5" s="45"/>
+      <c r="B5" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="43">
         <v>1.0</v>
       </c>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="38"/>
     </row>
     <row r="6">
-      <c r="A6" s="44"/>
-      <c r="B6" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="42">
+      <c r="A6" s="45"/>
+      <c r="B6" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="43">
         <v>1.0</v>
       </c>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
     </row>
     <row r="7">
-      <c r="A7" s="45"/>
-      <c r="B7" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" s="42">
+      <c r="A7" s="46"/>
+      <c r="B7" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="43">
         <v>1.0</v>
       </c>
-      <c r="D7" s="46">
+      <c r="D7" s="47">
         <f>COUNTIF(B2:B7,"&lt;&gt;text")</f>
         <v>6</v>
       </c>
-      <c r="E7" s="46">
+      <c r="E7" s="47">
         <f>(SUM(C2:C7)/D7)*10</f>
         <v>10</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="48" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="49">
+      <c r="A8" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="45"/>
+      <c r="B9" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="50">
+        <v>0.0</v>
+      </c>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="45"/>
+      <c r="B10" s="49" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="45"/>
+      <c r="B11" s="49" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="50">
+        <v>0.0</v>
+      </c>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="45"/>
+      <c r="B12" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="45"/>
+      <c r="B13" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="51">
         <v>1.0</v>
       </c>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="44"/>
-      <c r="B9" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="49">
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="45"/>
+      <c r="B14" s="49" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="51">
         <v>1.0</v>
       </c>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="44"/>
-      <c r="B10" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="49">
-        <v>1.0</v>
-      </c>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="44"/>
-      <c r="B11" s="48" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="49">
-        <v>1.0</v>
-      </c>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="44"/>
-      <c r="B12" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="49">
-        <v>1.0</v>
-      </c>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="44"/>
-      <c r="B13" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="49">
-        <v>1.0</v>
-      </c>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="44"/>
-      <c r="B14" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="49">
-        <v>1.0</v>
-      </c>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
     </row>
     <row r="15">
-      <c r="A15" s="44"/>
-      <c r="B15" s="48" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="49">
-        <v>1.0</v>
-      </c>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
+      <c r="A15" s="45"/>
+      <c r="B15" s="49" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
     </row>
     <row r="16">
-      <c r="A16" s="44"/>
-      <c r="B16" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="C16" s="49">
-        <v>1.0</v>
-      </c>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
+      <c r="A16" s="45"/>
+      <c r="B16" s="49" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="50">
+        <v>0.0</v>
+      </c>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
     </row>
     <row r="17">
-      <c r="A17" s="44"/>
-      <c r="B17" s="48" t="s">
-        <v>42</v>
-      </c>
-      <c r="C17" s="49">
-        <v>1.0</v>
-      </c>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
+      <c r="A17" s="45"/>
+      <c r="B17" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
     </row>
     <row r="18">
-      <c r="A18" s="44"/>
-      <c r="B18" s="48" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="49">
-        <v>1.0</v>
-      </c>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
+      <c r="A18" s="45"/>
+      <c r="B18" s="49" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
     </row>
     <row r="19">
-      <c r="A19" s="45"/>
-      <c r="B19" s="48" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="49">
-        <v>1.0</v>
-      </c>
-      <c r="D19" s="46">
+      <c r="A19" s="46"/>
+      <c r="B19" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="D19" s="47">
         <f>COUNTIF(B8:B19,"&lt;&gt;text")</f>
         <v>12</v>
       </c>
-      <c r="E19" s="46">
+      <c r="E19" s="47">
         <f>(SUM(C8:C19)/D19)*10</f>
-        <v>10</v>
+        <v>4.583333333</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="50" t="s">
-        <v>45</v>
-      </c>
-      <c r="B20" s="51" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="52">
+      <c r="A20" s="52" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="53" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="54">
         <v>1.0</v>
       </c>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
     </row>
     <row r="21">
-      <c r="A21" s="44"/>
-      <c r="B21" s="51" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="52">
+      <c r="A21" s="45"/>
+      <c r="B21" s="53" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="55">
+        <v>0.0</v>
+      </c>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="45"/>
+      <c r="B22" s="53" t="s">
+        <v>51</v>
+      </c>
+      <c r="C22" s="55">
+        <v>0.5</v>
+      </c>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="45"/>
+      <c r="B23" s="53" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="55">
+        <v>0.0</v>
+      </c>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="44"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="45"/>
+      <c r="B24" s="53" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="55">
+        <v>0.5</v>
+      </c>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="44"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="46"/>
+      <c r="B25" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="54">
         <v>1.0</v>
       </c>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="44"/>
-      <c r="B22" s="51" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" s="52">
-        <v>1.0</v>
-      </c>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="44"/>
-      <c r="B23" s="51" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="52">
-        <v>1.0</v>
-      </c>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="43"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="44"/>
-      <c r="B24" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24" s="52">
-        <v>1.0</v>
-      </c>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="43"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="45"/>
-      <c r="B25" s="51" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="52">
-        <v>1.0</v>
-      </c>
-      <c r="D25" s="53">
+      <c r="D25" s="56">
         <f>COUNTIF(B20:B25,"&lt;&gt;text")</f>
         <v>6</v>
       </c>
-      <c r="E25" s="53">
+      <c r="E25" s="56">
         <f>(SUM(C20:C25)/D25)*10</f>
-        <v>10</v>
-      </c>
-      <c r="F25" s="43"/>
+        <v>5</v>
+      </c>
+      <c r="F25" s="44"/>
     </row>
     <row r="26">
-      <c r="A26" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="55" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" s="56">
+      <c r="A26" s="57" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" s="58" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="59">
         <v>1.0</v>
       </c>
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="43"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="44"/>
     </row>
     <row r="27">
-      <c r="A27" s="44"/>
-      <c r="B27" s="55" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="56">
+      <c r="A27" s="45"/>
+      <c r="B27" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="59">
         <v>1.0</v>
       </c>
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="43"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="44"/>
     </row>
     <row r="28">
-      <c r="A28" s="45"/>
-      <c r="B28" s="55" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="56">
-        <v>1.0</v>
-      </c>
-      <c r="D28" s="53">
+      <c r="A28" s="46"/>
+      <c r="B28" s="58" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="60">
+        <v>0.0</v>
+      </c>
+      <c r="D28" s="56">
         <f>COUNTIF(B26:B28,"&lt;&gt;text")</f>
         <v>3</v>
       </c>
-      <c r="E28" s="53">
+      <c r="E28" s="56">
         <f>(SUM(C26:C28)/D28)*10</f>
-        <v>10</v>
-      </c>
-      <c r="F28" s="43"/>
+        <v>6.666666667</v>
+      </c>
+      <c r="F28" s="44"/>
     </row>
     <row r="29">
-      <c r="B29" s="57">
+      <c r="B29" s="61">
         <f>COUNTIF(B2:B28,"&lt;&gt;text")</f>
         <v>27</v>
       </c>
-      <c r="C29" s="57">
+      <c r="C29" s="61">
         <f>(SUM(C2:C28)/B29)*10</f>
-        <v>10</v>
+        <v>6.111111111</v>
       </c>
     </row>
   </sheetData>
